--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
@@ -270,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -357,6 +357,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -853,7 +856,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Toda sexta, atualize o valor atual (os números vêm dos painéis das planilhas de origem ou do Painel da clínica, 17) e copie para a coluna da semana em Semanas. O Painel mostra o resumo por objetivo e a lista completa com semáforo. No exemplo, S1 a S11 são as sextas de 03/07 a 11/09/2026.</t>
+          <t>Toda sexta, atualize o valor atual (os números vêm do Painel da clínica, 17, ou dos painéis das planilhas de origem) e copie para a coluna da semana em Semanas. Semana sem número: escreva "—", não 0. O Painel mostra o resumo por objetivo e a lista completa com semáforo. No exemplo, S1 a S11 são as sextas de 03/07 a 11/09/2026.</t>
         </is>
       </c>
     </row>
@@ -865,7 +868,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Sexta-feira, 10 minutos: atualizar os valores. Primeira segunda do mês: reunião de 20 minutos entre os sócios olhando o Painel.</t>
+          <t>Esta é uma planilha MENSAL. Na sexta, os valores já estão no Painel da clínica (17), que você atualiza em 3 minutos: copiar o número de cada resultado-chave para a coluna da semana em Semanas leva menos de um minuto e cabe nessa mesma parada. A conversa sobre as metas é mensal: primeira segunda do mês, 20 minutos entre os sócios olhando o Painel.</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1040,7 @@
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
         <f>COUNTIFS(Metas!$J$5:$J$13,"Atingido")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
@@ -1047,7 +1050,7 @@
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
         <f>IFERROR(AVERAGEIFS(Metas!$H$5:$H$13,Metas!$B$5:$B$13,"&lt;&gt;"),0)</f>
-        <v>0.34526330440098</v>
+        <v>0.452190287203573</v>
       </c>
       <c r="H5" s="14" t="n"/>
     </row>
@@ -1104,11 +1107,11 @@
       </c>
       <c r="C9" s="25">
         <f>IF(OR(Metas!$A$5="",B9=0),"",AVERAGEIFS(Metas!$H$5:$H$7,Metas!$B$5:$B$7,"&lt;&gt;"))</f>
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="D9" s="24">
         <f>IF(Metas!$A$5="","",COUNTIFS(Metas!$J$5:$J$7,"Atingido"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="24">
         <f>IF(Metas!$A$5="","",COUNTIFS(Metas!$J$5:$J$7,"Em risco"))</f>
@@ -1116,7 +1119,7 @@
       </c>
       <c r="F9" s="26" t="str">
         <f>IF(C9="","",REPT("█",ROUND(C9*30,0)))</f>
-        <v>█████████</v>
+        <v>██████████</v>
       </c>
       <c r="G9" s="21" t="n"/>
       <c r="H9" s="22" t="n"/>
@@ -1160,7 +1163,7 @@
       </c>
       <c r="C11" s="25">
         <f>IF(OR(Metas!$A$11="",B11=0),"",AVERAGEIFS(Metas!$H$11:$H$13,Metas!$B$11:$B$13,"&lt;&gt;"))</f>
-        <v>0.447890126422557</v>
+        <v>0.727004408163668</v>
       </c>
       <c r="D11" s="24">
         <f>IF(Metas!$A$11="","",COUNTIFS(Metas!$J$11:$J$13,"Atingido"))</f>
@@ -1172,7 +1175,7 @@
       </c>
       <c r="F11" s="26" t="str">
         <f>IF(C11="","",REPT("█",ROUND(C11*30,0)))</f>
-        <v>█████████████</v>
+        <v>██████████████████████</v>
       </c>
       <c r="G11" s="21" t="n"/>
       <c r="H11" s="22" t="n"/>
@@ -1306,7 +1309,7 @@
       </c>
       <c r="C17" s="28">
         <f>IF(Metas!B7="","",Metas!G7)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="28">
         <f>IF(Metas!B7="","",Metas!F7)</f>
@@ -1314,7 +1317,7 @@
       </c>
       <c r="E17" s="25">
         <f>IF(Metas!B7="","",Metas!H7)</f>
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="F17" s="25">
         <f>IF(Metas!B7="","",Metas!I7)</f>
@@ -1322,11 +1325,11 @@
       </c>
       <c r="G17" s="24" t="str">
         <f>IF(Metas!B7="","",Metas!J7)</f>
-        <v>No ritmo</v>
+        <v>Atingido</v>
       </c>
       <c r="H17" s="26" t="str">
         <f>IF(E17="","",REPT("█",ROUND(E17*20,0)))</f>
-        <v>██████████████████</v>
+        <v>████████████████████</v>
       </c>
     </row>
     <row r="18">
@@ -1442,7 +1445,7 @@
       </c>
       <c r="C21" s="28">
         <f>IF(Metas!B11="","",Metas!G11)</f>
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
       <c r="D21" s="28">
         <f>IF(Metas!B11="","",Metas!F11)</f>
@@ -1450,7 +1453,7 @@
       </c>
       <c r="E21" s="25">
         <f>IF(Metas!B11="","",Metas!H11)</f>
-        <v>0</v>
+        <v>0.517241379310345</v>
       </c>
       <c r="F21" s="25">
         <f>IF(Metas!B11="","",Metas!I11)</f>
@@ -1460,9 +1463,9 @@
         <f>IF(Metas!B11="","",Metas!J11)</f>
         <v>Em risco</v>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="26" t="str">
         <f>IF(E21="","",REPT("█",ROUND(E21*20,0)))</f>
-        <v/>
+        <v>██████████</v>
       </c>
     </row>
     <row r="22">
@@ -1514,11 +1517,11 @@
       </c>
       <c r="D23" s="28">
         <f>IF(Metas!B13="","",Metas!F13)</f>
-        <v>21937</v>
+        <v>17527</v>
       </c>
       <c r="E23" s="25">
         <f>IF(Metas!B13="","",Metas!H13)</f>
-        <v>0.677003712601005</v>
+        <v>0.997105178513992</v>
       </c>
       <c r="F23" s="25">
         <f>IF(Metas!B13="","",Metas!I13)</f>
@@ -1526,11 +1529,11 @@
       </c>
       <c r="G23" s="24" t="str">
         <f>IF(Metas!B13="","",Metas!J13)</f>
-        <v>Atenção</v>
+        <v>No ritmo</v>
       </c>
       <c r="H23" s="26" t="str">
         <f>IF(E23="","",REPT("█",ROUND(E23*20,0)))</f>
-        <v>██████████████</v>
+        <v>████████████████████</v>
       </c>
     </row>
     <row r="24"/>
@@ -1913,7 +1916,7 @@
       </c>
       <c r="L5" s="35" t="inlineStr">
         <is>
-          <t>Painel da planilha 01 (horas atendidas ÷ disponíveis). Partida = primeira sexta de julho; atual = 4 semanas até 11/09.</t>
+          <t>Horas atendidas ÷ disponíveis nas 4 semanas até a sexta (Agenda da planilha 01). Partida = sexta 03/07, que olha 06/06 a 03/07: a agenda da 01 começa em 01/06, então dá para refazer a conta.</t>
         </is>
       </c>
     </row>
@@ -1990,11 +1993,11 @@
         <v>8</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="25">
         <f>IF(B7="","",IF(F7=E7,"",IF(K7="Menor é melhor",MAX(0,MIN(1,(E7-G7)/(E7-F7))),MAX(0,MIN(1,(G7-E7)/(F7-E7))))))</f>
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="I7" s="25">
         <f>IF(B7="","",Config!$B$10)</f>
@@ -2002,7 +2005,7 @@
       </c>
       <c r="J7" s="24" t="str">
         <f>IF(OR(B7="",H7=""),"",IF(H7&gt;=1,"Atingido",IF(H7&gt;=I7-0.1,"No ritmo",IF(H7&gt;=I7-0.25,"Atenção","Em risco"))))</f>
-        <v>No ritmo</v>
+        <v>Atingido</v>
       </c>
       <c r="K7" s="36" t="inlineStr">
         <is>
@@ -2113,7 +2116,7 @@
       </c>
       <c r="L9" s="35" t="inlineStr">
         <is>
-          <t>Dias entre o envio e o pagamento dos lotes pagos no trimestre (Lotes da 13). Partida = média de janeiro a junho. Cobrar o convênio na sexta quando a previsão passar.</t>
+          <t>Dias entre o envio e o pagamento dos lotes pagos no trimestre (aba Lotes da 13, colunas Data de envio e Data do pagamento). Partida = mesma conta nos lotes pagos de janeiro a junho, que estão na mesma aba. Semana sem lote pago fica "—".</t>
         </is>
       </c>
     </row>
@@ -2188,17 +2191,17 @@
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>9.5</v>
+        <v>10.9</v>
       </c>
       <c r="F11" s="36" t="n">
         <v>8</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
       <c r="H11" s="25">
         <f>IF(B11="","",IF(F11=E11,"",IF(K11="Menor é melhor",MAX(0,MIN(1,(E11-G11)/(E11-F11))),MAX(0,MIN(1,(G11-E11)/(F11-E11))))))</f>
-        <v>0</v>
+        <v>0.517241379310345</v>
       </c>
       <c r="I11" s="25">
         <f>IF(B11="","",Config!$B$10)</f>
@@ -2289,14 +2292,14 @@
         <v>8200</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>21937</v>
+        <v>17527</v>
       </c>
       <c r="G13" s="36" t="n">
         <v>17500</v>
       </c>
       <c r="H13" s="25">
         <f>IF(B13="","",IF(F13=E13,"",IF(K13="Menor é melhor",MAX(0,MIN(1,(E13-G13)/(E13-F13))),MAX(0,MIN(1,(G13-E13)/(F13-E13))))))</f>
-        <v>0.677003712601005</v>
+        <v>0.997105178513992</v>
       </c>
       <c r="I13" s="25">
         <f>IF(B13="","",Config!$B$10)</f>
@@ -2304,7 +2307,7 @@
       </c>
       <c r="J13" s="24" t="str">
         <f>IF(OR(B13="",H13=""),"",IF(H13&gt;=1,"Atingido",IF(H13&gt;=I13-0.1,"No ritmo",IF(H13&gt;=I13-0.25,"Atenção","Em risco"))))</f>
-        <v>Atenção</v>
+        <v>No ritmo</v>
       </c>
       <c r="K13" s="36" t="inlineStr">
         <is>
@@ -2313,7 +2316,7 @@
       </c>
       <c r="L13" s="35" t="inlineStr">
         <is>
-          <t>Meta = saldo provisionado de setembro na planilha 10; atual = o que já está na conta separada (planilha 12).</t>
+          <t>Meta = saldo provisionado de AGOSTO na planilha 10 (último mês fechado; o de setembro ainda muda até o dia 30). Atual = o que já está na conta separada (planilha 12).</t>
         </is>
       </c>
     </row>
@@ -2597,25 +2600,25 @@
         <v>0</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N7" s="36" t="n"/>
       <c r="O7" s="36" t="n"/>
@@ -2674,8 +2677,10 @@
         <f>IF(Metas!B9="","",Metas!F9)</f>
         <v>40</v>
       </c>
-      <c r="C9" s="36" t="n">
-        <v>0</v>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D9" s="36" t="n">
         <v>46.5</v>
@@ -2765,37 +2770,37 @@
         <v>8</v>
       </c>
       <c r="C11" s="36" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="F11" s="36" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G11" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="G11" s="36" t="n">
-        <v>9.6</v>
-      </c>
       <c r="H11" s="36" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J11" s="36" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="K11" s="36" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L11" s="36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M11" s="36" t="n">
         <v>9.4</v>
-      </c>
-      <c r="K11" s="36" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="L11" s="36" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="M11" s="36" t="n">
-        <v>10.4</v>
       </c>
       <c r="N11" s="36" t="n"/>
       <c r="O11" s="36" t="n"/>
@@ -2852,7 +2857,7 @@
       </c>
       <c r="B13" s="24">
         <f>IF(Metas!B13="","",Metas!F13)</f>
-        <v>21937</v>
+        <v>17527</v>
       </c>
       <c r="C13" s="36" t="n">
         <v>8200</v>
@@ -2890,16 +2895,17 @@
       <c r="N13" s="36" t="n"/>
       <c r="O13" s="36" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>A coluna da semana atual fica destacada. Valores em % são digitados como 16,8 (não 0,168). No exemplo, S1 a S11 são as sextas de 03/07 a 11/09/2026.</t>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="39" t="inlineStr">
+        <is>
+          <t>A coluna da semana atual fica destacada. Valores em % são digitados como 16,8 (não 0,168). Semana sem nada a medir: escreva "—" (não escreva 0, que puxa a série para baixo como se o resultado tivesse desabado). No exemplo, S1 a S11 são as sextas de 03/07 a 11/09/2026, e o prazo real dos lotes fica "—" na S1 porque nenhum lote foi pago naquela semana do trimestre.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A15:O15"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
@@ -791,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -952,17 +952,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1050,7 +1062,7 @@
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
         <f>IFERROR(AVERAGEIFS(Metas!$H$5:$H$13,Metas!$B$5:$B$13,"&lt;&gt;"),0)</f>
-        <v>0.452190287203573</v>
+        <v>0.444641239882311</v>
       </c>
       <c r="H5" s="14" t="n"/>
     </row>
@@ -1163,7 +1175,7 @@
       </c>
       <c r="C11" s="25">
         <f>IF(OR(Metas!$A$11="",B11=0),"",AVERAGEIFS(Metas!$H$11:$H$13,Metas!$B$11:$B$13,"&lt;&gt;"))</f>
-        <v>0.727004408163668</v>
+        <v>0.704357266199884</v>
       </c>
       <c r="D11" s="24">
         <f>IF(Metas!$A$11="","",COUNTIFS(Metas!$J$11:$J$13,"Atingido"))</f>
@@ -1175,7 +1187,7 @@
       </c>
       <c r="F11" s="26" t="str">
         <f>IF(C11="","",REPT("█",ROUND(C11*30,0)))</f>
-        <v>██████████████████████</v>
+        <v>█████████████████████</v>
       </c>
       <c r="G11" s="21" t="n"/>
       <c r="H11" s="22" t="n"/>
@@ -1517,11 +1529,11 @@
       </c>
       <c r="D23" s="28">
         <f>IF(Metas!B13="","",Metas!F13)</f>
-        <v>17527</v>
+        <v>18209</v>
       </c>
       <c r="E23" s="25">
         <f>IF(Metas!B13="","",Metas!H13)</f>
-        <v>0.997105178513992</v>
+        <v>0.92916375262264</v>
       </c>
       <c r="F23" s="25">
         <f>IF(Metas!B13="","",Metas!I13)</f>
@@ -1533,7 +1545,7 @@
       </c>
       <c r="H23" s="26" t="str">
         <f>IF(E23="","",REPT("█",ROUND(E23*20,0)))</f>
-        <v>████████████████████</v>
+        <v>███████████████████</v>
       </c>
     </row>
     <row r="24"/>
@@ -1661,9 +1673,8 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B8" s="33">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B8" s="33" t="n">
+        <v>46279</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -2292,14 +2303,14 @@
         <v>8200</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>17527</v>
+        <v>18209</v>
       </c>
       <c r="G13" s="36" t="n">
         <v>17500</v>
       </c>
       <c r="H13" s="25">
         <f>IF(B13="","",IF(F13=E13,"",IF(K13="Menor é melhor",MAX(0,MIN(1,(E13-G13)/(E13-F13))),MAX(0,MIN(1,(G13-E13)/(F13-E13))))))</f>
-        <v>0.997105178513992</v>
+        <v>0.92916375262264</v>
       </c>
       <c r="I13" s="25">
         <f>IF(B13="","",Config!$B$10)</f>
@@ -2857,7 +2868,7 @@
       </c>
       <c r="B13" s="24">
         <f>IF(Metas!B13="","",Metas!F13)</f>
-        <v>17527</v>
+        <v>18209</v>
       </c>
       <c r="C13" s="36" t="n">
         <v>8200</v>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
@@ -2376,7 +2376,7 @@
     <dataValidation sqref="C5:C13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$B$13,0,0,MAX(1,COUNTA(Config!$B$13:$B$24)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:G13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal"/>
+    <dataValidation sqref="E5:G13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Em Config, preencha o trimestre, as datas de início e fim, deixe a data de referência em =HOJE() e liste as pessoas da clínica (de cima para baixo, sem pular linha).</t>
+          <t>Em Config, preencha o trimestre, as datas de início e fim, troque a data de referência por =HOJE() (no exemplo ela está congelada em 14/09/2026) e liste as pessoas da clínica (de cima para baixo, sem pular linha).</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
@@ -940,7 +940,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
   </mergeCells>
   <conditionalFormatting sqref="C4:O4">
     <cfRule type="expression" priority="1" dxfId="4">
-      <formula>COLUMN()-2=Config!$B$9</formula>
+      <formula>COLUMN()-2=INDIRECT("Config!$B$9")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
@@ -1909,7 +1909,7 @@
         <v>74.5</v>
       </c>
       <c r="H5" s="25">
-        <f>IF(B5="","",IF(F5=E5,"",IF(K5="Menor é melhor",MAX(0,MIN(1,(E5-G5)/(E5-F5))),MAX(0,MIN(1,(G5-E5)/(F5-E5))))))</f>
+        <f>IF(OR(B5="",G5=""),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),IF(G5=0,0,MAX(0,F5/G5)))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),IF(F5=0,0,MAX(0,G5/F5))))))</f>
         <v>0</v>
       </c>
       <c r="I5" s="25">
@@ -1958,7 +1958,7 @@
         <v>7.1</v>
       </c>
       <c r="H6" s="25">
-        <f>IF(B6="","",IF(F6=E6,"",IF(K6="Menor é melhor",MAX(0,MIN(1,(E6-G6)/(E6-F6))),MAX(0,MIN(1,(G6-E6)/(F6-E6))))))</f>
+        <f>IF(OR(B6="",G6=""),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),IF(G6=0,0,MAX(0,F6/G6)))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),IF(F6=0,0,MAX(0,G6/F6))))))</f>
         <v>0</v>
       </c>
       <c r="I6" s="25">
@@ -2007,7 +2007,7 @@
         <v>8</v>
       </c>
       <c r="H7" s="25">
-        <f>IF(B7="","",IF(F7=E7,"",IF(K7="Menor é melhor",MAX(0,MIN(1,(E7-G7)/(E7-F7))),MAX(0,MIN(1,(G7-E7)/(F7-E7))))))</f>
+        <f>IF(OR(B7="",G7=""),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),IF(G7=0,0,MAX(0,F7/G7)))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),IF(F7=0,0,MAX(0,G7/F7))))))</f>
         <v>1</v>
       </c>
       <c r="I7" s="25">
@@ -2060,7 +2060,7 @@
         <v>5.5</v>
       </c>
       <c r="H8" s="25">
-        <f>IF(B8="","",IF(F8=E8,"",IF(K8="Menor é melhor",MAX(0,MIN(1,(E8-G8)/(E8-F8))),MAX(0,MIN(1,(G8-E8)/(F8-E8))))))</f>
+        <f>IF(OR(B8="",G8=""),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),IF(G8=0,0,MAX(0,F8/G8)))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),IF(F8=0,0,MAX(0,G8/F8))))))</f>
         <v>0.285714285714286</v>
       </c>
       <c r="I8" s="25">
@@ -2109,7 +2109,7 @@
         <v>44</v>
       </c>
       <c r="H9" s="25">
-        <f>IF(B9="","",IF(F9=E9,"",IF(K9="Menor é melhor",MAX(0,MIN(1,(E9-G9)/(E9-F9))),MAX(0,MIN(1,(G9-E9)/(F9-E9))))))</f>
+        <f>IF(OR(B9="",G9=""),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),IF(G9=0,0,MAX(0,F9/G9)))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),IF(F9=0,0,MAX(0,G9/F9))))))</f>
         <v>0.402985074626866</v>
       </c>
       <c r="I9" s="25">
@@ -2158,7 +2158,7 @@
         <v>200</v>
       </c>
       <c r="H10" s="25">
-        <f>IF(B10="","",IF(F10=E10,"",IF(K10="Menor é melhor",MAX(0,MIN(1,(E10-G10)/(E10-F10))),MAX(0,MIN(1,(G10-E10)/(F10-E10))))))</f>
+        <f>IF(OR(B10="",G10=""),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),IF(G10=0,0,MAX(0,F10/G10)))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),IF(F10=0,0,MAX(0,G10/F10))))))</f>
         <v>0.2</v>
       </c>
       <c r="I10" s="25">
@@ -2211,7 +2211,7 @@
         <v>9.4</v>
       </c>
       <c r="H11" s="25">
-        <f>IF(B11="","",IF(F11=E11,"",IF(K11="Menor é melhor",MAX(0,MIN(1,(E11-G11)/(E11-F11))),MAX(0,MIN(1,(G11-E11)/(F11-E11))))))</f>
+        <f>IF(OR(B11="",G11=""),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),IF(G11=0,0,MAX(0,F11/G11)))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),IF(F11=0,0,MAX(0,G11/F11))))))</f>
         <v>0.517241379310345</v>
       </c>
       <c r="I11" s="25">
@@ -2260,7 +2260,7 @@
         <v>14000</v>
       </c>
       <c r="H12" s="25">
-        <f>IF(B12="","",IF(F12=E12,"",IF(K12="Menor é melhor",MAX(0,MIN(1,(E12-G12)/(E12-F12))),MAX(0,MIN(1,(G12-E12)/(F12-E12))))))</f>
+        <f>IF(OR(B12="",G12=""),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),IF(G12=0,0,MAX(0,F12/G12)))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),IF(F12=0,0,MAX(0,G12/F12))))))</f>
         <v>0.666666666666667</v>
       </c>
       <c r="I12" s="25">
@@ -2309,7 +2309,7 @@
         <v>17500</v>
       </c>
       <c r="H13" s="25">
-        <f>IF(B13="","",IF(F13=E13,"",IF(K13="Menor é melhor",MAX(0,MIN(1,(E13-G13)/(E13-F13))),MAX(0,MIN(1,(G13-E13)/(F13-E13))))))</f>
+        <f>IF(OR(B13="",G13=""),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),IF(G13=0,0,MAX(0,F13/G13)))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),IF(F13=0,0,MAX(0,G13/F13))))))</f>
         <v>0.92916375262264</v>
       </c>
       <c r="I13" s="25">
@@ -2334,7 +2334,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso). A planilha avisa; a ação é da clínica.</t>
+          <t>Progresso: valor atual no alvo = 100 %; fora do alvo, é o caminho andado entre o ponto de partida e a meta — e, quando o ponto de partida já estava dentro da meta (um teto ou piso a manter), é meta ÷ atual (16 pacientes para um teto de 8 = 50 %). Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso). A planilha avisa; a ação é da clínica.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
@@ -365,7 +365,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <color rgb="008A86A0"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00EDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1579,15 +1591,18 @@
   </mergeCells>
   <conditionalFormatting sqref="G15:G23">
     <cfRule type="expression" priority="1" dxfId="0">
+      <formula>G15="Faltam dados"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>G15="Atingido"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>G15="No ritmo"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="4" dxfId="3">
       <formula>G15="Atenção"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="5" dxfId="4">
       <formula>G15="Em risco"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1909,7 +1924,7 @@
         <v>74.5</v>
       </c>
       <c r="H5" s="25">
-        <f>IF(OR(B5="",G5=""),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),IF(G5=0,0,MAX(0,F5/G5)))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),IF(F5=0,0,MAX(0,G5/F5))))))</f>
+        <f>IF(B5="","",IF(OR(NOT(ISNUMBER(E5)),NOT(ISNUMBER(F5)),NOT(ISNUMBER(G5))),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),MAX(0,1-(G5-F5)/MAX(ABS(F5),ABS(G5))))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),MAX(0,1-(F5-G5)/MAX(ABS(F5),ABS(G5))))))))</f>
         <v>0</v>
       </c>
       <c r="I5" s="25">
@@ -1917,7 +1932,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J5" s="24" t="str">
-        <f>IF(OR(B5="",H5=""),"",IF(H5&gt;=1,"Atingido",IF(H5&gt;=I5-0.1,"No ritmo",IF(H5&gt;=I5-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B5="","",IF(H5="","Faltam dados",IF(H5&gt;=1,"Atingido",IF(H5&gt;=I5-0.1,"No ritmo",IF(H5&gt;=I5-0.25,"Atenção","Em risco")))))</f>
         <v>Em risco</v>
       </c>
       <c r="K5" s="36" t="inlineStr">
@@ -1958,7 +1973,7 @@
         <v>7.1</v>
       </c>
       <c r="H6" s="25">
-        <f>IF(OR(B6="",G6=""),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),IF(G6=0,0,MAX(0,F6/G6)))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),IF(F6=0,0,MAX(0,G6/F6))))))</f>
+        <f>IF(B6="","",IF(OR(NOT(ISNUMBER(E6)),NOT(ISNUMBER(F6)),NOT(ISNUMBER(G6))),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),MAX(0,1-(G6-F6)/MAX(ABS(F6),ABS(G6))))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),MAX(0,1-(F6-G6)/MAX(ABS(F6),ABS(G6))))))))</f>
         <v>0</v>
       </c>
       <c r="I6" s="25">
@@ -1966,7 +1981,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J6" s="24" t="str">
-        <f>IF(OR(B6="",H6=""),"",IF(H6&gt;=1,"Atingido",IF(H6&gt;=I6-0.1,"No ritmo",IF(H6&gt;=I6-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B6="","",IF(H6="","Faltam dados",IF(H6&gt;=1,"Atingido",IF(H6&gt;=I6-0.1,"No ritmo",IF(H6&gt;=I6-0.25,"Atenção","Em risco")))))</f>
         <v>Em risco</v>
       </c>
       <c r="K6" s="36" t="inlineStr">
@@ -2007,7 +2022,7 @@
         <v>8</v>
       </c>
       <c r="H7" s="25">
-        <f>IF(OR(B7="",G7=""),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),IF(G7=0,0,MAX(0,F7/G7)))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),IF(F7=0,0,MAX(0,G7/F7))))))</f>
+        <f>IF(B7="","",IF(OR(NOT(ISNUMBER(E7)),NOT(ISNUMBER(F7)),NOT(ISNUMBER(G7))),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),MAX(0,1-(G7-F7)/MAX(ABS(F7),ABS(G7))))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),MAX(0,1-(F7-G7)/MAX(ABS(F7),ABS(G7))))))))</f>
         <v>1</v>
       </c>
       <c r="I7" s="25">
@@ -2015,7 +2030,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J7" s="24" t="str">
-        <f>IF(OR(B7="",H7=""),"",IF(H7&gt;=1,"Atingido",IF(H7&gt;=I7-0.1,"No ritmo",IF(H7&gt;=I7-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B7="","",IF(H7="","Faltam dados",IF(H7&gt;=1,"Atingido",IF(H7&gt;=I7-0.1,"No ritmo",IF(H7&gt;=I7-0.25,"Atenção","Em risco")))))</f>
         <v>Atingido</v>
       </c>
       <c r="K7" s="36" t="inlineStr">
@@ -2060,7 +2075,7 @@
         <v>5.5</v>
       </c>
       <c r="H8" s="25">
-        <f>IF(OR(B8="",G8=""),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),IF(G8=0,0,MAX(0,F8/G8)))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),IF(F8=0,0,MAX(0,G8/F8))))))</f>
+        <f>IF(B8="","",IF(OR(NOT(ISNUMBER(E8)),NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),MAX(0,1-(G8-F8)/MAX(ABS(F8),ABS(G8))))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),MAX(0,1-(F8-G8)/MAX(ABS(F8),ABS(G8))))))))</f>
         <v>0.285714285714286</v>
       </c>
       <c r="I8" s="25">
@@ -2068,7 +2083,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J8" s="24" t="str">
-        <f>IF(OR(B8="",H8=""),"",IF(H8&gt;=1,"Atingido",IF(H8&gt;=I8-0.1,"No ritmo",IF(H8&gt;=I8-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B8="","",IF(H8="","Faltam dados",IF(H8&gt;=1,"Atingido",IF(H8&gt;=I8-0.1,"No ritmo",IF(H8&gt;=I8-0.25,"Atenção","Em risco")))))</f>
         <v>Em risco</v>
       </c>
       <c r="K8" s="36" t="inlineStr">
@@ -2109,7 +2124,7 @@
         <v>44</v>
       </c>
       <c r="H9" s="25">
-        <f>IF(OR(B9="",G9=""),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),IF(G9=0,0,MAX(0,F9/G9)))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),IF(F9=0,0,MAX(0,G9/F9))))))</f>
+        <f>IF(B9="","",IF(OR(NOT(ISNUMBER(E9)),NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),MAX(0,1-(G9-F9)/MAX(ABS(F9),ABS(G9))))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),MAX(0,1-(F9-G9)/MAX(ABS(F9),ABS(G9))))))))</f>
         <v>0.402985074626866</v>
       </c>
       <c r="I9" s="25">
@@ -2117,7 +2132,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J9" s="24" t="str">
-        <f>IF(OR(B9="",H9=""),"",IF(H9&gt;=1,"Atingido",IF(H9&gt;=I9-0.1,"No ritmo",IF(H9&gt;=I9-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B9="","",IF(H9="","Faltam dados",IF(H9&gt;=1,"Atingido",IF(H9&gt;=I9-0.1,"No ritmo",IF(H9&gt;=I9-0.25,"Atenção","Em risco")))))</f>
         <v>Em risco</v>
       </c>
       <c r="K9" s="36" t="inlineStr">
@@ -2158,7 +2173,7 @@
         <v>200</v>
       </c>
       <c r="H10" s="25">
-        <f>IF(OR(B10="",G10=""),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),IF(G10=0,0,MAX(0,F10/G10)))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),IF(F10=0,0,MAX(0,G10/F10))))))</f>
+        <f>IF(B10="","",IF(OR(NOT(ISNUMBER(E10)),NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),MAX(0,1-(G10-F10)/MAX(ABS(F10),ABS(G10))))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),MAX(0,1-(F10-G10)/MAX(ABS(F10),ABS(G10))))))))</f>
         <v>0.2</v>
       </c>
       <c r="I10" s="25">
@@ -2166,7 +2181,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J10" s="24" t="str">
-        <f>IF(OR(B10="",H10=""),"",IF(H10&gt;=1,"Atingido",IF(H10&gt;=I10-0.1,"No ritmo",IF(H10&gt;=I10-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B10="","",IF(H10="","Faltam dados",IF(H10&gt;=1,"Atingido",IF(H10&gt;=I10-0.1,"No ritmo",IF(H10&gt;=I10-0.25,"Atenção","Em risco")))))</f>
         <v>Em risco</v>
       </c>
       <c r="K10" s="36" t="inlineStr">
@@ -2211,7 +2226,7 @@
         <v>9.4</v>
       </c>
       <c r="H11" s="25">
-        <f>IF(OR(B11="",G11=""),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),IF(G11=0,0,MAX(0,F11/G11)))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),IF(F11=0,0,MAX(0,G11/F11))))))</f>
+        <f>IF(B11="","",IF(OR(NOT(ISNUMBER(E11)),NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),MAX(0,1-(G11-F11)/MAX(ABS(F11),ABS(G11))))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),MAX(0,1-(F11-G11)/MAX(ABS(F11),ABS(G11))))))))</f>
         <v>0.517241379310345</v>
       </c>
       <c r="I11" s="25">
@@ -2219,7 +2234,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J11" s="24" t="str">
-        <f>IF(OR(B11="",H11=""),"",IF(H11&gt;=1,"Atingido",IF(H11&gt;=I11-0.1,"No ritmo",IF(H11&gt;=I11-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B11="","",IF(H11="","Faltam dados",IF(H11&gt;=1,"Atingido",IF(H11&gt;=I11-0.1,"No ritmo",IF(H11&gt;=I11-0.25,"Atenção","Em risco")))))</f>
         <v>Em risco</v>
       </c>
       <c r="K11" s="36" t="inlineStr">
@@ -2260,7 +2275,7 @@
         <v>14000</v>
       </c>
       <c r="H12" s="25">
-        <f>IF(OR(B12="",G12=""),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),IF(G12=0,0,MAX(0,F12/G12)))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),IF(F12=0,0,MAX(0,G12/F12))))))</f>
+        <f>IF(B12="","",IF(OR(NOT(ISNUMBER(E12)),NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),MAX(0,1-(G12-F12)/MAX(ABS(F12),ABS(G12))))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),MAX(0,1-(F12-G12)/MAX(ABS(F12),ABS(G12))))))))</f>
         <v>0.666666666666667</v>
       </c>
       <c r="I12" s="25">
@@ -2268,7 +2283,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J12" s="24" t="str">
-        <f>IF(OR(B12="",H12=""),"",IF(H12&gt;=1,"Atingido",IF(H12&gt;=I12-0.1,"No ritmo",IF(H12&gt;=I12-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B12="","",IF(H12="","Faltam dados",IF(H12&gt;=1,"Atingido",IF(H12&gt;=I12-0.1,"No ritmo",IF(H12&gt;=I12-0.25,"Atenção","Em risco")))))</f>
         <v>Atenção</v>
       </c>
       <c r="K12" s="36" t="inlineStr">
@@ -2309,7 +2324,7 @@
         <v>17500</v>
       </c>
       <c r="H13" s="25">
-        <f>IF(OR(B13="",G13=""),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),IF(G13=0,0,MAX(0,F13/G13)))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),IF(F13=0,0,MAX(0,G13/F13))))))</f>
+        <f>IF(B13="","",IF(OR(NOT(ISNUMBER(E13)),NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),MAX(0,1-(G13-F13)/MAX(ABS(F13),ABS(G13))))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),MAX(0,1-(F13-G13)/MAX(ABS(F13),ABS(G13))))))))</f>
         <v>0.92916375262264</v>
       </c>
       <c r="I13" s="25">
@@ -2317,7 +2332,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J13" s="24" t="str">
-        <f>IF(OR(B13="",H13=""),"",IF(H13&gt;=1,"Atingido",IF(H13&gt;=I13-0.1,"No ritmo",IF(H13&gt;=I13-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B13="","",IF(H13="","Faltam dados",IF(H13&gt;=1,"Atingido",IF(H13&gt;=I13-0.1,"No ritmo",IF(H13&gt;=I13-0.25,"Atenção","Em risco")))))</f>
         <v>No ritmo</v>
       </c>
       <c r="K13" s="36" t="inlineStr">
@@ -2334,7 +2349,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Progresso: valor atual no alvo = 100 %; fora do alvo, é o caminho andado entre o ponto de partida e a meta — e, quando o ponto de partida já estava dentro da meta (um teto ou piso a manter), é meta ÷ atual (16 pacientes para um teto de 8 = 50 %). Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso). A planilha avisa; a ação é da clínica.</t>
+          <t>Progresso: só é calculado com ponto de partida, meta e valor atual preenchidos (zero vale; vazio vira "Faltam dados" e fica fora das contagens). Valor atual no alvo = 100 %. Fora do alvo, é o caminho andado entre o ponto de partida e a meta; quando o ponto de partida já estava dentro da meta (um limite a manter), é a distância ao limite: para um teto ("Menor é melhor"), meta ÷ atual (16 para um teto de 8 = 50 %); para um piso ("Maior é melhor"), atual ÷ meta (4 para um piso de 8 = 50 %). Com zero ou valores negativos (um limite de prejuízo, por exemplo) a conta usa o maior valor absoluto como escala e nunca dá 100 % sem o alvo estar cumprido. Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso). A planilha avisa; a ação é da clínica.</t>
         </is>
       </c>
     </row>
@@ -2357,15 +2372,18 @@
   </mergeCells>
   <conditionalFormatting sqref="J5:J13">
     <cfRule type="expression" priority="1" dxfId="0">
+      <formula>J5="Faltam dados"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>J5="Atingido"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>J5="No ritmo"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="4" dxfId="3">
       <formula>J5="Atenção"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="5" dxfId="4">
       <formula>J5="Em risco"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2921,7 +2939,7 @@
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:O4">
-    <cfRule type="expression" priority="1" dxfId="4">
+    <cfRule type="expression" priority="1" dxfId="5">
       <formula>COLUMN()-2=INDIRECT("Config!$B$9")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
@@ -1073,7 +1073,7 @@
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
-        <f>IFERROR(AVERAGEIFS(Metas!$H$5:$H$13,Metas!$B$5:$B$13,"&lt;&gt;"),0)</f>
+        <f>IF(COUNT(Metas!$H$5:$H$13)=0,"Faltam dados",AVERAGEIFS(Metas!$H$5:$H$13,Metas!$B$5:$B$13,"&lt;&gt;"))</f>
         <v>0.444641239882311</v>
       </c>
       <c r="H5" s="14" t="n"/>
@@ -1130,7 +1130,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="25">
-        <f>IF(OR(Metas!$A$5="",B9=0),"",AVERAGEIFS(Metas!$H$5:$H$7,Metas!$B$5:$B$7,"&lt;&gt;"))</f>
+        <f>IF(OR(Metas!$A$5="",B9=0),"",IF(COUNT(Metas!$H$5:$H$7)=0,"Faltam dados",AVERAGEIFS(Metas!$H$5:$H$7,Metas!$B$5:$B$7,"&lt;&gt;")))</f>
         <v>0.333333333333333</v>
       </c>
       <c r="D9" s="24">
@@ -1142,7 +1142,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="26" t="str">
-        <f>IF(C9="","",REPT("█",ROUND(C9*30,0)))</f>
+        <f>IF(ISNUMBER(C9),REPT("█",ROUND(C9*30,0)),"")</f>
         <v>██████████</v>
       </c>
       <c r="G9" s="21" t="n"/>
@@ -1158,7 +1158,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="25">
-        <f>IF(OR(Metas!$A$8="",B10=0),"",AVERAGEIFS(Metas!$H$8:$H$10,Metas!$B$8:$B$10,"&lt;&gt;"))</f>
+        <f>IF(OR(Metas!$A$8="",B10=0),"",IF(COUNT(Metas!$H$8:$H$10)=0,"Faltam dados",AVERAGEIFS(Metas!$H$8:$H$10,Metas!$B$8:$B$10,"&lt;&gt;")))</f>
         <v>0.296233120113717</v>
       </c>
       <c r="D10" s="24">
@@ -1170,7 +1170,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="26" t="str">
-        <f>IF(C10="","",REPT("█",ROUND(C10*30,0)))</f>
+        <f>IF(ISNUMBER(C10),REPT("█",ROUND(C10*30,0)),"")</f>
         <v>█████████</v>
       </c>
       <c r="G10" s="21" t="n"/>
@@ -1186,7 +1186,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="25">
-        <f>IF(OR(Metas!$A$11="",B11=0),"",AVERAGEIFS(Metas!$H$11:$H$13,Metas!$B$11:$B$13,"&lt;&gt;"))</f>
+        <f>IF(OR(Metas!$A$11="",B11=0),"",IF(COUNT(Metas!$H$11:$H$13)=0,"Faltam dados",AVERAGEIFS(Metas!$H$11:$H$13,Metas!$B$11:$B$13,"&lt;&gt;")))</f>
         <v>0.704357266199884</v>
       </c>
       <c r="D11" s="24">
@@ -1198,7 +1198,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="26" t="str">
-        <f>IF(C11="","",REPT("█",ROUND(C11*30,0)))</f>
+        <f>IF(ISNUMBER(C11),REPT("█",ROUND(C11*30,0)),"")</f>
         <v>█████████████████████</v>
       </c>
       <c r="G11" s="21" t="n"/>
@@ -1924,7 +1924,7 @@
         <v>74.5</v>
       </c>
       <c r="H5" s="25">
-        <f>IF(B5="","",IF(OR(NOT(ISNUMBER(E5)),NOT(ISNUMBER(F5)),NOT(ISNUMBER(G5))),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),MAX(0,1-(G5-F5)/MAX(ABS(F5),ABS(G5))))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),MAX(0,1-(F5-G5)/MAX(ABS(F5),ABS(G5))))))))</f>
+        <f>IF(B5="","",IF(OR(NOT(ISNUMBER(E5)),NOT(ISNUMBER(F5)),NOT(ISNUMBER(G5)),AND(K5&lt;&gt;"Menor é melhor",K5&lt;&gt;"Maior é melhor")),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),MAX(0,1-(G5-F5)/MAX(ABS(F5),ABS(G5))))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),MAX(0,1-(F5-G5)/MAX(ABS(F5),ABS(G5))))))))</f>
         <v>0</v>
       </c>
       <c r="I5" s="25">
@@ -1973,7 +1973,7 @@
         <v>7.1</v>
       </c>
       <c r="H6" s="25">
-        <f>IF(B6="","",IF(OR(NOT(ISNUMBER(E6)),NOT(ISNUMBER(F6)),NOT(ISNUMBER(G6))),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),MAX(0,1-(G6-F6)/MAX(ABS(F6),ABS(G6))))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),MAX(0,1-(F6-G6)/MAX(ABS(F6),ABS(G6))))))))</f>
+        <f>IF(B6="","",IF(OR(NOT(ISNUMBER(E6)),NOT(ISNUMBER(F6)),NOT(ISNUMBER(G6)),AND(K6&lt;&gt;"Menor é melhor",K6&lt;&gt;"Maior é melhor")),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),MAX(0,1-(G6-F6)/MAX(ABS(F6),ABS(G6))))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),MAX(0,1-(F6-G6)/MAX(ABS(F6),ABS(G6))))))))</f>
         <v>0</v>
       </c>
       <c r="I6" s="25">
@@ -2022,7 +2022,7 @@
         <v>8</v>
       </c>
       <c r="H7" s="25">
-        <f>IF(B7="","",IF(OR(NOT(ISNUMBER(E7)),NOT(ISNUMBER(F7)),NOT(ISNUMBER(G7))),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),MAX(0,1-(G7-F7)/MAX(ABS(F7),ABS(G7))))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),MAX(0,1-(F7-G7)/MAX(ABS(F7),ABS(G7))))))))</f>
+        <f>IF(B7="","",IF(OR(NOT(ISNUMBER(E7)),NOT(ISNUMBER(F7)),NOT(ISNUMBER(G7)),AND(K7&lt;&gt;"Menor é melhor",K7&lt;&gt;"Maior é melhor")),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),MAX(0,1-(G7-F7)/MAX(ABS(F7),ABS(G7))))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),MAX(0,1-(F7-G7)/MAX(ABS(F7),ABS(G7))))))))</f>
         <v>1</v>
       </c>
       <c r="I7" s="25">
@@ -2075,7 +2075,7 @@
         <v>5.5</v>
       </c>
       <c r="H8" s="25">
-        <f>IF(B8="","",IF(OR(NOT(ISNUMBER(E8)),NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),MAX(0,1-(G8-F8)/MAX(ABS(F8),ABS(G8))))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),MAX(0,1-(F8-G8)/MAX(ABS(F8),ABS(G8))))))))</f>
+        <f>IF(B8="","",IF(OR(NOT(ISNUMBER(E8)),NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8)),AND(K8&lt;&gt;"Menor é melhor",K8&lt;&gt;"Maior é melhor")),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),MAX(0,1-(G8-F8)/MAX(ABS(F8),ABS(G8))))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),MAX(0,1-(F8-G8)/MAX(ABS(F8),ABS(G8))))))))</f>
         <v>0.285714285714286</v>
       </c>
       <c r="I8" s="25">
@@ -2124,7 +2124,7 @@
         <v>44</v>
       </c>
       <c r="H9" s="25">
-        <f>IF(B9="","",IF(OR(NOT(ISNUMBER(E9)),NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),MAX(0,1-(G9-F9)/MAX(ABS(F9),ABS(G9))))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),MAX(0,1-(F9-G9)/MAX(ABS(F9),ABS(G9))))))))</f>
+        <f>IF(B9="","",IF(OR(NOT(ISNUMBER(E9)),NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9)),AND(K9&lt;&gt;"Menor é melhor",K9&lt;&gt;"Maior é melhor")),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),MAX(0,1-(G9-F9)/MAX(ABS(F9),ABS(G9))))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),MAX(0,1-(F9-G9)/MAX(ABS(F9),ABS(G9))))))))</f>
         <v>0.402985074626866</v>
       </c>
       <c r="I9" s="25">
@@ -2173,7 +2173,7 @@
         <v>200</v>
       </c>
       <c r="H10" s="25">
-        <f>IF(B10="","",IF(OR(NOT(ISNUMBER(E10)),NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),MAX(0,1-(G10-F10)/MAX(ABS(F10),ABS(G10))))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),MAX(0,1-(F10-G10)/MAX(ABS(F10),ABS(G10))))))))</f>
+        <f>IF(B10="","",IF(OR(NOT(ISNUMBER(E10)),NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10)),AND(K10&lt;&gt;"Menor é melhor",K10&lt;&gt;"Maior é melhor")),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),MAX(0,1-(G10-F10)/MAX(ABS(F10),ABS(G10))))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),MAX(0,1-(F10-G10)/MAX(ABS(F10),ABS(G10))))))))</f>
         <v>0.2</v>
       </c>
       <c r="I10" s="25">
@@ -2226,7 +2226,7 @@
         <v>9.4</v>
       </c>
       <c r="H11" s="25">
-        <f>IF(B11="","",IF(OR(NOT(ISNUMBER(E11)),NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),MAX(0,1-(G11-F11)/MAX(ABS(F11),ABS(G11))))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),MAX(0,1-(F11-G11)/MAX(ABS(F11),ABS(G11))))))))</f>
+        <f>IF(B11="","",IF(OR(NOT(ISNUMBER(E11)),NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11)),AND(K11&lt;&gt;"Menor é melhor",K11&lt;&gt;"Maior é melhor")),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),MAX(0,1-(G11-F11)/MAX(ABS(F11),ABS(G11))))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),MAX(0,1-(F11-G11)/MAX(ABS(F11),ABS(G11))))))))</f>
         <v>0.517241379310345</v>
       </c>
       <c r="I11" s="25">
@@ -2275,7 +2275,7 @@
         <v>14000</v>
       </c>
       <c r="H12" s="25">
-        <f>IF(B12="","",IF(OR(NOT(ISNUMBER(E12)),NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),MAX(0,1-(G12-F12)/MAX(ABS(F12),ABS(G12))))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),MAX(0,1-(F12-G12)/MAX(ABS(F12),ABS(G12))))))))</f>
+        <f>IF(B12="","",IF(OR(NOT(ISNUMBER(E12)),NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12)),AND(K12&lt;&gt;"Menor é melhor",K12&lt;&gt;"Maior é melhor")),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),MAX(0,1-(G12-F12)/MAX(ABS(F12),ABS(G12))))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),MAX(0,1-(F12-G12)/MAX(ABS(F12),ABS(G12))))))))</f>
         <v>0.666666666666667</v>
       </c>
       <c r="I12" s="25">
@@ -2324,7 +2324,7 @@
         <v>17500</v>
       </c>
       <c r="H13" s="25">
-        <f>IF(B13="","",IF(OR(NOT(ISNUMBER(E13)),NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),MAX(0,1-(G13-F13)/MAX(ABS(F13),ABS(G13))))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),MAX(0,1-(F13-G13)/MAX(ABS(F13),ABS(G13))))))))</f>
+        <f>IF(B13="","",IF(OR(NOT(ISNUMBER(E13)),NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13)),AND(K13&lt;&gt;"Menor é melhor",K13&lt;&gt;"Maior é melhor")),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),MAX(0,1-(G13-F13)/MAX(ABS(F13),ABS(G13))))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),MAX(0,1-(F13-G13)/MAX(ABS(F13),ABS(G13))))))))</f>
         <v>0.92916375262264</v>
       </c>
       <c r="I13" s="25">
@@ -2349,7 +2349,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Progresso: só é calculado com ponto de partida, meta e valor atual preenchidos (zero vale; vazio vira "Faltam dados" e fica fora das contagens). Valor atual no alvo = 100 %. Fora do alvo, é o caminho andado entre o ponto de partida e a meta; quando o ponto de partida já estava dentro da meta (um limite a manter), é a distância ao limite: para um teto ("Menor é melhor"), meta ÷ atual (16 para um teto de 8 = 50 %); para um piso ("Maior é melhor"), atual ÷ meta (4 para um piso de 8 = 50 %). Com zero ou valores negativos (um limite de prejuízo, por exemplo) a conta usa o maior valor absoluto como escala e nunca dá 100 % sem o alvo estar cumprido. Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso). A planilha avisa; a ação é da clínica.</t>
+          <t>Progresso: só é calculado com ponto de partida, meta, valor atual e sentido preenchidos (zero vale; vazio vira "Faltam dados" e fica fora das contagens; sem nenhuma medição, a média do Painel também diz "Faltam dados"). Valor atual no alvo = 100 %. Fora do alvo, é o caminho andado entre o ponto de partida e a meta; quando o ponto de partida já estava dentro da meta (um limite a manter), é a distância ao limite: para um teto ("Menor é melhor"), meta ÷ atual (16 para um teto de 8 = 50 %); para um piso ("Maior é melhor"), atual ÷ meta (4 para um piso de 8 = 50 %). Com zero ou valores negativos (um limite de prejuízo, por exemplo) a conta usa o maior valor absoluto como escala e nunca dá 100 % sem o alvo estar cumprido. Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso). A planilha avisa; a ação é da clínica.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
@@ -1264,11 +1264,11 @@
         <v>Bruna Carvalho</v>
       </c>
       <c r="C15" s="28">
-        <f>IF(Metas!B5="","",Metas!G5)</f>
+        <f>IF(OR(Metas!B5="",NOT(ISNUMBER(Metas!G5))),"",Metas!G5)</f>
         <v>74.5</v>
       </c>
       <c r="D15" s="28">
-        <f>IF(Metas!B5="","",Metas!F5)</f>
+        <f>IF(OR(Metas!B5="",NOT(ISNUMBER(Metas!F5))),"",Metas!F5)</f>
         <v>80</v>
       </c>
       <c r="E15" s="25">
@@ -1298,11 +1298,11 @@
         <v>Bruna Carvalho</v>
       </c>
       <c r="C16" s="28">
-        <f>IF(Metas!B6="","",Metas!G6)</f>
+        <f>IF(OR(Metas!B6="",NOT(ISNUMBER(Metas!G6))),"",Metas!G6)</f>
         <v>7.1</v>
       </c>
       <c r="D16" s="28">
-        <f>IF(Metas!B6="","",Metas!F6)</f>
+        <f>IF(OR(Metas!B6="",NOT(ISNUMBER(Metas!F6))),"",Metas!F6)</f>
         <v>5</v>
       </c>
       <c r="E16" s="25">
@@ -1332,11 +1332,11 @@
         <v>Bruna Carvalho</v>
       </c>
       <c r="C17" s="28">
-        <f>IF(Metas!B7="","",Metas!G7)</f>
+        <f>IF(OR(Metas!B7="",NOT(ISNUMBER(Metas!G7))),"",Metas!G7)</f>
         <v>8</v>
       </c>
       <c r="D17" s="28">
-        <f>IF(Metas!B7="","",Metas!F7)</f>
+        <f>IF(OR(Metas!B7="",NOT(ISNUMBER(Metas!F7))),"",Metas!F7)</f>
         <v>8</v>
       </c>
       <c r="E17" s="25">
@@ -1366,11 +1366,11 @@
         <v>Dr. Paulo Andrade</v>
       </c>
       <c r="C18" s="28">
-        <f>IF(Metas!B8="","",Metas!G8)</f>
+        <f>IF(OR(Metas!B8="",NOT(ISNUMBER(Metas!G8))),"",Metas!G8)</f>
         <v>5.5</v>
       </c>
       <c r="D18" s="28">
-        <f>IF(Metas!B8="","",Metas!F8)</f>
+        <f>IF(OR(Metas!B8="",NOT(ISNUMBER(Metas!F8))),"",Metas!F8)</f>
         <v>4</v>
       </c>
       <c r="E18" s="25">
@@ -1400,11 +1400,11 @@
         <v>Dr. Paulo Andrade</v>
       </c>
       <c r="C19" s="28">
-        <f>IF(Metas!B9="","",Metas!G9)</f>
+        <f>IF(OR(Metas!B9="",NOT(ISNUMBER(Metas!G9))),"",Metas!G9)</f>
         <v>44</v>
       </c>
       <c r="D19" s="28">
-        <f>IF(Metas!B9="","",Metas!F9)</f>
+        <f>IF(OR(Metas!B9="",NOT(ISNUMBER(Metas!F9))),"",Metas!F9)</f>
         <v>40</v>
       </c>
       <c r="E19" s="25">
@@ -1434,11 +1434,11 @@
         <v>Dr. Paulo Andrade</v>
       </c>
       <c r="C20" s="28">
-        <f>IF(Metas!B10="","",Metas!G10)</f>
+        <f>IF(OR(Metas!B10="",NOT(ISNUMBER(Metas!G10))),"",Metas!G10)</f>
         <v>200</v>
       </c>
       <c r="D20" s="28">
-        <f>IF(Metas!B10="","",Metas!F10)</f>
+        <f>IF(OR(Metas!B10="",NOT(ISNUMBER(Metas!F10))),"",Metas!F10)</f>
         <v>1000</v>
       </c>
       <c r="E20" s="25">
@@ -1468,11 +1468,11 @@
         <v>Dra. Carolina Mendes</v>
       </c>
       <c r="C21" s="28">
-        <f>IF(Metas!B11="","",Metas!G11)</f>
+        <f>IF(OR(Metas!B11="",NOT(ISNUMBER(Metas!G11))),"",Metas!G11)</f>
         <v>9.4</v>
       </c>
       <c r="D21" s="28">
-        <f>IF(Metas!B11="","",Metas!F11)</f>
+        <f>IF(OR(Metas!B11="",NOT(ISNUMBER(Metas!F11))),"",Metas!F11)</f>
         <v>8</v>
       </c>
       <c r="E21" s="25">
@@ -1502,11 +1502,11 @@
         <v>Dra. Carolina Mendes</v>
       </c>
       <c r="C22" s="28">
-        <f>IF(Metas!B12="","",Metas!G12)</f>
+        <f>IF(OR(Metas!B12="",NOT(ISNUMBER(Metas!G12))),"",Metas!G12)</f>
         <v>14000</v>
       </c>
       <c r="D22" s="28">
-        <f>IF(Metas!B12="","",Metas!F12)</f>
+        <f>IF(OR(Metas!B12="",NOT(ISNUMBER(Metas!F12))),"",Metas!F12)</f>
         <v>17000</v>
       </c>
       <c r="E22" s="25">
@@ -1536,11 +1536,11 @@
         <v>Dra. Carolina Mendes</v>
       </c>
       <c r="C23" s="28">
-        <f>IF(Metas!B13="","",Metas!G13)</f>
+        <f>IF(OR(Metas!B13="",NOT(ISNUMBER(Metas!G13))),"",Metas!G13)</f>
         <v>17500</v>
       </c>
       <c r="D23" s="28">
-        <f>IF(Metas!B13="","",Metas!F13)</f>
+        <f>IF(OR(Metas!B13="",NOT(ISNUMBER(Metas!F13))),"",Metas!F13)</f>
         <v>18209</v>
       </c>
       <c r="E23" s="25">
@@ -2523,7 +2523,7 @@
         <v>Ocupação da agenda nas últimas 4 semanas (%)</v>
       </c>
       <c r="B5" s="24">
-        <f>IF(Metas!B5="","",Metas!F5)</f>
+        <f>IF(OR(Metas!B5="",NOT(ISNUMBER(Metas!F5))),"",Metas!F5)</f>
         <v>80</v>
       </c>
       <c r="C5" s="36" t="n">
@@ -2568,7 +2568,7 @@
         <v>Taxa de falta nas últimas 4 semanas (%)</v>
       </c>
       <c r="B6" s="24">
-        <f>IF(Metas!B6="","",Metas!F6)</f>
+        <f>IF(OR(Metas!B6="",NOT(ISNUMBER(Metas!F6))),"",Metas!F6)</f>
         <v>5</v>
       </c>
       <c r="C6" s="36" t="n">
@@ -2613,7 +2613,7 @@
         <v>Pacientes na lista de retorno sem agendamento</v>
       </c>
       <c r="B7" s="24">
-        <f>IF(Metas!B7="","",Metas!F7)</f>
+        <f>IF(OR(Metas!B7="",NOT(ISNUMBER(Metas!F7))),"",Metas!F7)</f>
         <v>8</v>
       </c>
       <c r="C7" s="36" t="n">
@@ -2658,7 +2658,7 @@
         <v>Glosa nos lotes pagos no ano (%)</v>
       </c>
       <c r="B8" s="24">
-        <f>IF(Metas!B8="","",Metas!F8)</f>
+        <f>IF(OR(Metas!B8="",NOT(ISNUMBER(Metas!F8))),"",Metas!F8)</f>
         <v>4</v>
       </c>
       <c r="C8" s="36" t="n">
@@ -2703,7 +2703,7 @@
         <v>Prazo real médio de pagamento dos lotes (dias)</v>
       </c>
       <c r="B9" s="24">
-        <f>IF(Metas!B9="","",Metas!F9)</f>
+        <f>IF(OR(Metas!B9="",NOT(ISNUMBER(Metas!F9))),"",Metas!F9)</f>
         <v>40</v>
       </c>
       <c r="C9" s="36" t="inlineStr">
@@ -2750,7 +2750,7 @@
         <v>Glosa recuperada por recurso no trimestre (R$)</v>
       </c>
       <c r="B10" s="24">
-        <f>IF(Metas!B10="","",Metas!F10)</f>
+        <f>IF(OR(Metas!B10="",NOT(ISNUMBER(Metas!F10))),"",Metas!F10)</f>
         <v>1000</v>
       </c>
       <c r="C10" s="36" t="n">
@@ -2795,7 +2795,7 @@
         <v>Inadimplência a prazo: vencido ÷ (pago + vencido) (%)</v>
       </c>
       <c r="B11" s="24">
-        <f>IF(Metas!B11="","",Metas!F11)</f>
+        <f>IF(OR(Metas!B11="",NOT(ISNUMBER(Metas!F11))),"",Metas!F11)</f>
         <v>8</v>
       </c>
       <c r="C11" s="36" t="n">
@@ -2840,7 +2840,7 @@
         <v>Reserva guardada em conta separada (R$)</v>
       </c>
       <c r="B12" s="24">
-        <f>IF(Metas!B12="","",Metas!F12)</f>
+        <f>IF(OR(Metas!B12="",NOT(ISNUMBER(Metas!F12))),"",Metas!F12)</f>
         <v>17000</v>
       </c>
       <c r="C12" s="36" t="n">
@@ -2885,7 +2885,7 @@
         <v>Conta de provisão de impostos, 13º e férias (R$)</v>
       </c>
       <c r="B13" s="24">
-        <f>IF(Metas!B13="","",Metas!F13)</f>
+        <f>IF(OR(Metas!B13="",NOT(ISNUMBER(Metas!F13))),"",Metas!F13)</f>
         <v>18209</v>
       </c>
       <c r="C13" s="36" t="n">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
@@ -1260,7 +1260,7 @@
         <v>Ocupação da agenda nas últimas 4 semanas (%)</v>
       </c>
       <c r="B15" s="24" t="str">
-        <f>IF(Metas!B5="","",Metas!C5)</f>
+        <f>IF(OR(Metas!B5="",Metas!C5=""),"",Metas!C5)</f>
         <v>Bruna Carvalho</v>
       </c>
       <c r="C15" s="28">
@@ -1294,7 +1294,7 @@
         <v>Taxa de falta nas últimas 4 semanas (%)</v>
       </c>
       <c r="B16" s="24" t="str">
-        <f>IF(Metas!B6="","",Metas!C6)</f>
+        <f>IF(OR(Metas!B6="",Metas!C6=""),"",Metas!C6)</f>
         <v>Bruna Carvalho</v>
       </c>
       <c r="C16" s="28">
@@ -1328,7 +1328,7 @@
         <v>Pacientes na lista de retorno sem agendamento</v>
       </c>
       <c r="B17" s="24" t="str">
-        <f>IF(Metas!B7="","",Metas!C7)</f>
+        <f>IF(OR(Metas!B7="",Metas!C7=""),"",Metas!C7)</f>
         <v>Bruna Carvalho</v>
       </c>
       <c r="C17" s="28">
@@ -1362,7 +1362,7 @@
         <v>Glosa nos lotes pagos no ano (%)</v>
       </c>
       <c r="B18" s="24" t="str">
-        <f>IF(Metas!B8="","",Metas!C8)</f>
+        <f>IF(OR(Metas!B8="",Metas!C8=""),"",Metas!C8)</f>
         <v>Dr. Paulo Andrade</v>
       </c>
       <c r="C18" s="28">
@@ -1396,7 +1396,7 @@
         <v>Prazo real médio de pagamento dos lotes (dias)</v>
       </c>
       <c r="B19" s="24" t="str">
-        <f>IF(Metas!B9="","",Metas!C9)</f>
+        <f>IF(OR(Metas!B9="",Metas!C9=""),"",Metas!C9)</f>
         <v>Dr. Paulo Andrade</v>
       </c>
       <c r="C19" s="28">
@@ -1430,7 +1430,7 @@
         <v>Glosa recuperada por recurso no trimestre (R$)</v>
       </c>
       <c r="B20" s="24" t="str">
-        <f>IF(Metas!B10="","",Metas!C10)</f>
+        <f>IF(OR(Metas!B10="",Metas!C10=""),"",Metas!C10)</f>
         <v>Dr. Paulo Andrade</v>
       </c>
       <c r="C20" s="28">
@@ -1464,7 +1464,7 @@
         <v>Inadimplência a prazo: vencido ÷ (pago + vencido) (%)</v>
       </c>
       <c r="B21" s="24" t="str">
-        <f>IF(Metas!B11="","",Metas!C11)</f>
+        <f>IF(OR(Metas!B11="",Metas!C11=""),"",Metas!C11)</f>
         <v>Dra. Carolina Mendes</v>
       </c>
       <c r="C21" s="28">
@@ -1498,7 +1498,7 @@
         <v>Reserva guardada em conta separada (R$)</v>
       </c>
       <c r="B22" s="24" t="str">
-        <f>IF(Metas!B12="","",Metas!C12)</f>
+        <f>IF(OR(Metas!B12="",Metas!C12=""),"",Metas!C12)</f>
         <v>Dra. Carolina Mendes</v>
       </c>
       <c r="C22" s="28">
@@ -1532,7 +1532,7 @@
         <v>Conta de provisão de impostos, 13º e férias (R$)</v>
       </c>
       <c r="B23" s="24" t="str">
-        <f>IF(Metas!B13="","",Metas!C13)</f>
+        <f>IF(OR(Metas!B13="",Metas!C13=""),"",Metas!C13)</f>
         <v>Dra. Carolina Mendes</v>
       </c>
       <c r="C23" s="28">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/19-metas-do-trimestre.xlsx
@@ -824,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -952,7 +953,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e semáforos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
